--- a/data/trans_orig/IP74A2_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP74A2_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto el alquiler en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos del alquiler en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
